--- a/mapaEstudopromotoresautoservico.xlsx
+++ b/mapaEstudopromotoresautoservico.xlsx
@@ -1,29 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC 0025\Desktop\Estudo roteiro promotores  autoserviço\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A26761F1-7CD7-4FF0-A4DE-A7AD178022FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95EF9829-2724-4678-8F7C-2503CEFD2655}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{6E192D0C-ECB7-41D4-A2D6-1793BFCFF8CB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{6E192D0C-ECB7-41D4-A2D6-1793BFCFF8CB}"/>
   </bookViews>
   <sheets>
-    <sheet name="Promotores" sheetId="1" r:id="rId1"/>
-    <sheet name="Coordenadas lojas" sheetId="2" r:id="rId2"/>
-    <sheet name="BasePromotores" sheetId="4" r:id="rId3"/>
-    <sheet name="Planilha3" sheetId="3" r:id="rId4"/>
+    <sheet name="Promotores Autoserviço" sheetId="1" r:id="rId1"/>
+    <sheet name="ferias" sheetId="5" r:id="rId2"/>
+    <sheet name="Coordenadas lojas" sheetId="2" r:id="rId3"/>
+    <sheet name="BasePromotores" sheetId="4" r:id="rId4"/>
+    <sheet name="Planilha3" sheetId="3" r:id="rId5"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId5"/>
+    <externalReference r:id="rId6"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Promotores!$A$1:$G$133</definedName>
-    <definedName name="DadosExternos_1" localSheetId="2" hidden="1">BasePromotores!$A$1:$D$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Promotores Autoserviço'!$A$1:$G$133</definedName>
+    <definedName name="DadosExternos_1" localSheetId="3" hidden="1">BasePromotores!$A$1:$D$22</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8957" uniqueCount="4455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9190" uniqueCount="4473">
   <si>
     <t>Bruno Alves</t>
   </si>
@@ -13408,13 +13409,67 @@
   </si>
   <si>
     <t>Joao makson Oliveira</t>
+  </si>
+  <si>
+    <t>Id</t>
+  </si>
+  <si>
+    <t>Promotor</t>
+  </si>
+  <si>
+    <t>CÓD</t>
+  </si>
+  <si>
+    <t>RAZAO SOCIAL</t>
+  </si>
+  <si>
+    <t>SEG</t>
+  </si>
+  <si>
+    <t>TER</t>
+  </si>
+  <si>
+    <t>QUA</t>
+  </si>
+  <si>
+    <t>QUI</t>
+  </si>
+  <si>
+    <t>SEX</t>
+  </si>
+  <si>
+    <t>SÁB</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>Mix de produtos quantidade</t>
+  </si>
+  <si>
+    <t>Rafael Gomes</t>
+  </si>
+  <si>
+    <t>Lucas Sátiro</t>
+  </si>
+  <si>
+    <t>Eduardo Davi Sousa</t>
+  </si>
+  <si>
+    <t>stenio douglas</t>
+  </si>
+  <si>
+    <t>Chandle Vital</t>
+  </si>
+  <si>
+    <t>Antônio Geam Ferreira</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -13437,8 +13492,19 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -13487,8 +13553,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF002060"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -13496,11 +13568,47 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -13533,9 +13641,38 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{43A55B2D-3BD5-4948-990D-77B086578BAF}"/>
   </cellStyles>
   <dxfs count="3">
     <dxf>
@@ -13582,9 +13719,9 @@
       <sheetName val="Planilha4"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2">
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1">
         <row r="1">
           <cell r="G1">
             <v>61</v>
@@ -17289,10 +17426,10 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -22059,6 +22196,561 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{418462FE-C0A7-46C9-9096-DC4172A1C354}">
+  <dimension ref="A3:L19"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="37.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" customWidth="1"/>
+    <col min="12" max="12" width="26.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="37.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="5"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="17"/>
+      <c r="I3" s="17"/>
+      <c r="J3" s="17"/>
+      <c r="K3" s="17"/>
+      <c r="L3" s="17"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E4" s="19">
+        <f>SUM(E6:E19)</f>
+        <v>7</v>
+      </c>
+      <c r="F4" s="19">
+        <f>SUM(F6:F19)</f>
+        <v>6</v>
+      </c>
+      <c r="G4" s="19">
+        <f t="shared" ref="G4:J4" si="0">SUM(G6:G19)</f>
+        <v>7</v>
+      </c>
+      <c r="H4" s="19">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="I4" s="19">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="J4" s="19">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="K4" s="19"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="16" t="s">
+        <v>4455</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>4456</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>4457</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>4458</v>
+      </c>
+      <c r="E5" s="20" t="s">
+        <v>4459</v>
+      </c>
+      <c r="F5" s="20" t="s">
+        <v>4460</v>
+      </c>
+      <c r="G5" s="20" t="s">
+        <v>4461</v>
+      </c>
+      <c r="H5" s="20" t="s">
+        <v>4462</v>
+      </c>
+      <c r="I5" s="20" t="s">
+        <v>4463</v>
+      </c>
+      <c r="J5" s="20" t="s">
+        <v>4464</v>
+      </c>
+      <c r="K5" s="20" t="s">
+        <v>4465</v>
+      </c>
+      <c r="L5" s="18" t="s">
+        <v>4466</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" s="14">
+        <v>10931</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>4439</v>
+      </c>
+      <c r="C6" s="14">
+        <v>8900011</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>3413</v>
+      </c>
+      <c r="E6" s="21">
+        <v>1</v>
+      </c>
+      <c r="F6" s="21"/>
+      <c r="G6" s="21">
+        <v>1</v>
+      </c>
+      <c r="H6" s="21"/>
+      <c r="I6" s="21">
+        <v>1</v>
+      </c>
+      <c r="J6" s="21"/>
+      <c r="K6" s="21">
+        <f>SUM(E6:J6)</f>
+        <v>3</v>
+      </c>
+      <c r="L6" s="14">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="14">
+        <v>10931</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>4439</v>
+      </c>
+      <c r="C7" s="14">
+        <v>663</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>261</v>
+      </c>
+      <c r="E7" s="21"/>
+      <c r="F7" s="21">
+        <v>1</v>
+      </c>
+      <c r="G7" s="21"/>
+      <c r="H7" s="21">
+        <v>1</v>
+      </c>
+      <c r="I7" s="21"/>
+      <c r="J7" s="21">
+        <v>1</v>
+      </c>
+      <c r="K7" s="21">
+        <f t="shared" ref="K7:K14" si="1">SUM(E7:J7)</f>
+        <v>3</v>
+      </c>
+      <c r="L7" s="14">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" s="15">
+        <v>10931</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>4439</v>
+      </c>
+      <c r="C8" s="15">
+        <v>192</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>3419</v>
+      </c>
+      <c r="E8" s="22">
+        <v>0</v>
+      </c>
+      <c r="F8" s="23"/>
+      <c r="G8" s="23">
+        <v>1</v>
+      </c>
+      <c r="H8" s="23"/>
+      <c r="I8" s="23"/>
+      <c r="J8" s="23"/>
+      <c r="K8" s="23">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="L8" s="15">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" s="14">
+        <v>10931</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>4439</v>
+      </c>
+      <c r="C9" s="14">
+        <v>9345</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>2141</v>
+      </c>
+      <c r="E9" s="21">
+        <v>1</v>
+      </c>
+      <c r="F9" s="21"/>
+      <c r="G9" s="21">
+        <v>1</v>
+      </c>
+      <c r="H9" s="21"/>
+      <c r="I9" s="21">
+        <v>1</v>
+      </c>
+      <c r="J9" s="21"/>
+      <c r="K9" s="21">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="L9" s="14">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" s="14">
+        <v>10931</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>4439</v>
+      </c>
+      <c r="C10" s="14">
+        <v>8900017</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>3417</v>
+      </c>
+      <c r="E10" s="21">
+        <v>1</v>
+      </c>
+      <c r="F10" s="21"/>
+      <c r="G10" s="21">
+        <v>1</v>
+      </c>
+      <c r="H10" s="21"/>
+      <c r="I10" s="21">
+        <v>1</v>
+      </c>
+      <c r="J10" s="21"/>
+      <c r="K10" s="21">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="L10" s="14">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" s="15">
+        <v>10931</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>4439</v>
+      </c>
+      <c r="C11" s="15">
+        <v>219</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>3418</v>
+      </c>
+      <c r="E11" s="23">
+        <v>1</v>
+      </c>
+      <c r="F11" s="23"/>
+      <c r="G11" s="23"/>
+      <c r="H11" s="23"/>
+      <c r="I11" s="22">
+        <v>0</v>
+      </c>
+      <c r="J11" s="23"/>
+      <c r="K11" s="23">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="L11" s="15">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" s="14">
+        <v>10931</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>4439</v>
+      </c>
+      <c r="C12" s="14">
+        <v>337</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="E12" s="21">
+        <v>1</v>
+      </c>
+      <c r="F12" s="21">
+        <v>0</v>
+      </c>
+      <c r="G12" s="21"/>
+      <c r="H12" s="21">
+        <v>1</v>
+      </c>
+      <c r="I12" s="21"/>
+      <c r="J12" s="21"/>
+      <c r="K12" s="21">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="L12" s="14">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" s="14">
+        <v>10931</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>4439</v>
+      </c>
+      <c r="C13" s="14">
+        <v>9622</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>2400</v>
+      </c>
+      <c r="E13" s="21"/>
+      <c r="F13" s="21">
+        <v>1</v>
+      </c>
+      <c r="G13" s="21"/>
+      <c r="H13" s="21">
+        <v>1</v>
+      </c>
+      <c r="I13" s="21"/>
+      <c r="J13" s="21">
+        <v>1</v>
+      </c>
+      <c r="K13" s="21">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="L13" s="14">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" s="14">
+        <v>10931</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>4439</v>
+      </c>
+      <c r="C14" s="14">
+        <v>11809</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>3002</v>
+      </c>
+      <c r="E14" s="21"/>
+      <c r="F14" s="21">
+        <v>1</v>
+      </c>
+      <c r="G14" s="21"/>
+      <c r="H14" s="21">
+        <v>1</v>
+      </c>
+      <c r="I14" s="21"/>
+      <c r="J14" s="21"/>
+      <c r="K14" s="21">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="L14" s="14">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" s="15">
+        <v>11587</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="C15" s="15">
+        <v>9342</v>
+      </c>
+      <c r="D15" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="E15" s="23"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="22">
+        <v>1</v>
+      </c>
+      <c r="H15" s="23"/>
+      <c r="I15" s="22">
+        <v>0</v>
+      </c>
+      <c r="J15" s="23"/>
+      <c r="K15" s="21">
+        <f>SUM(E15:J15)</f>
+        <v>1</v>
+      </c>
+      <c r="L15" s="15">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" s="14">
+        <v>11587</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C16" s="14">
+        <v>8971164</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="E16" s="21"/>
+      <c r="F16" s="21">
+        <v>1</v>
+      </c>
+      <c r="G16" s="21"/>
+      <c r="H16" s="21">
+        <v>1</v>
+      </c>
+      <c r="I16" s="21"/>
+      <c r="J16" s="21"/>
+      <c r="K16" s="21">
+        <f t="shared" ref="K16:K19" si="2">SUM(E16:J16)</f>
+        <v>2</v>
+      </c>
+      <c r="L16" s="14">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" s="14">
+        <v>11587</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C17" s="14">
+        <v>8971161</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="E17" s="21"/>
+      <c r="F17" s="21">
+        <v>1</v>
+      </c>
+      <c r="G17" s="21"/>
+      <c r="H17" s="21">
+        <v>1</v>
+      </c>
+      <c r="I17" s="21"/>
+      <c r="J17" s="21"/>
+      <c r="K17" s="21">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="L17" s="14">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" s="14">
+        <v>11587</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C18" s="14">
+        <v>1034</v>
+      </c>
+      <c r="D18" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="E18" s="21">
+        <v>1</v>
+      </c>
+      <c r="F18" s="21"/>
+      <c r="G18" s="21">
+        <v>1</v>
+      </c>
+      <c r="H18" s="21"/>
+      <c r="I18" s="21">
+        <v>1</v>
+      </c>
+      <c r="J18" s="21"/>
+      <c r="K18" s="21">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="L18" s="14">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" s="14">
+        <v>11587</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C19" s="14">
+        <v>11733</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="E19" s="21">
+        <v>1</v>
+      </c>
+      <c r="F19" s="21">
+        <v>1</v>
+      </c>
+      <c r="G19" s="21">
+        <v>1</v>
+      </c>
+      <c r="H19" s="21">
+        <v>1</v>
+      </c>
+      <c r="I19" s="21">
+        <v>1</v>
+      </c>
+      <c r="J19" s="21">
+        <v>1</v>
+      </c>
+      <c r="K19" s="21">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="L19" s="14">
+        <v>36</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.78740157480314965" bottom="0.78740157480314965" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" scale="80" orientation="landscape" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3C4332E-B84A-4982-B433-ACDB83F680D5}">
   <dimension ref="A1:D2869"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -62239,7 +62931,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDF024BF-359E-474E-BA76-40AC3F672C24}">
   <dimension ref="A1:D25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -62608,11 +63300,1705 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D42C2432-3E63-442F-A7E3-C385B16A6570}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:I96"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="4.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="4.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D1">
+        <f>SUM(D3:D18)</f>
+        <v>6</v>
+      </c>
+      <c r="E1">
+        <f t="shared" ref="E1:H1" si="0">SUM(E3:E18)</f>
+        <v>6</v>
+      </c>
+      <c r="F1">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="G1">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="H1">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="25" t="s">
+        <v>4456</v>
+      </c>
+      <c r="B2" s="25" t="s">
+        <v>4457</v>
+      </c>
+      <c r="C2" s="26" t="s">
+        <v>4458</v>
+      </c>
+      <c r="D2" s="26" t="s">
+        <v>4459</v>
+      </c>
+      <c r="E2" s="26" t="s">
+        <v>4460</v>
+      </c>
+      <c r="F2" s="26" t="s">
+        <v>4461</v>
+      </c>
+      <c r="G2" s="26" t="s">
+        <v>4462</v>
+      </c>
+      <c r="H2" s="26" t="s">
+        <v>4463</v>
+      </c>
+      <c r="I2" s="26" t="s">
+        <v>4464</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="27" t="s">
+        <v>4467</v>
+      </c>
+      <c r="B3" s="24">
+        <v>2990</v>
+      </c>
+      <c r="C3" t="s">
+        <v>1178</v>
+      </c>
+      <c r="D3" s="24">
+        <v>1</v>
+      </c>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24">
+        <v>1</v>
+      </c>
+      <c r="G3" s="24"/>
+      <c r="H3" s="24"/>
+      <c r="I3" s="24"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="27" t="s">
+        <v>4467</v>
+      </c>
+      <c r="B4" s="24">
+        <v>151</v>
+      </c>
+      <c r="C4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D4" s="24">
+        <v>1</v>
+      </c>
+      <c r="E4" s="24"/>
+      <c r="F4" s="24">
+        <v>1</v>
+      </c>
+      <c r="G4" s="24"/>
+      <c r="H4" s="24">
+        <v>1</v>
+      </c>
+      <c r="I4" s="24"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="27" t="s">
+        <v>4467</v>
+      </c>
+      <c r="B5" s="24">
+        <v>3968</v>
+      </c>
+      <c r="C5" t="s">
+        <v>1577</v>
+      </c>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="24">
+        <v>1</v>
+      </c>
+      <c r="G5" s="24"/>
+      <c r="H5" s="24"/>
+      <c r="I5" s="24"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="27" t="s">
+        <v>4467</v>
+      </c>
+      <c r="B6" s="24">
+        <v>830</v>
+      </c>
+      <c r="C6" t="s">
+        <v>367</v>
+      </c>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24">
+        <v>1</v>
+      </c>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24">
+        <v>1</v>
+      </c>
+      <c r="I6" s="24"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="27" t="s">
+        <v>4467</v>
+      </c>
+      <c r="B7" s="24">
+        <v>811</v>
+      </c>
+      <c r="C7" t="s">
+        <v>358</v>
+      </c>
+      <c r="D7" s="24"/>
+      <c r="E7" s="24">
+        <v>1</v>
+      </c>
+      <c r="F7" s="24"/>
+      <c r="G7" s="24">
+        <v>1</v>
+      </c>
+      <c r="H7" s="24"/>
+      <c r="I7" s="24"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="27" t="s">
+        <v>4467</v>
+      </c>
+      <c r="B8" s="24">
+        <v>3584</v>
+      </c>
+      <c r="C8" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D8" s="24">
+        <v>1</v>
+      </c>
+      <c r="E8" s="24"/>
+      <c r="F8" s="24"/>
+      <c r="G8" s="24">
+        <v>1</v>
+      </c>
+      <c r="H8" s="24"/>
+      <c r="I8" s="24"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="27" t="s">
+        <v>4467</v>
+      </c>
+      <c r="B9" s="24">
+        <v>348</v>
+      </c>
+      <c r="C9" t="s">
+        <v>142</v>
+      </c>
+      <c r="D9" s="24">
+        <v>1</v>
+      </c>
+      <c r="E9" s="24"/>
+      <c r="F9" s="24"/>
+      <c r="G9" s="24">
+        <v>1</v>
+      </c>
+      <c r="H9" s="24"/>
+      <c r="I9" s="24"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="27" t="s">
+        <v>4467</v>
+      </c>
+      <c r="B10" s="24">
+        <v>4786</v>
+      </c>
+      <c r="C10" t="s">
+        <v>1947</v>
+      </c>
+      <c r="D10" s="24">
+        <v>1</v>
+      </c>
+      <c r="E10" s="24"/>
+      <c r="F10" s="24"/>
+      <c r="G10" s="24">
+        <v>1</v>
+      </c>
+      <c r="H10" s="24"/>
+      <c r="I10" s="24"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="27" t="s">
+        <v>4467</v>
+      </c>
+      <c r="B11" s="24">
+        <v>840</v>
+      </c>
+      <c r="C11" t="s">
+        <v>385</v>
+      </c>
+      <c r="D11" s="24"/>
+      <c r="E11" s="24"/>
+      <c r="F11" s="24">
+        <v>1</v>
+      </c>
+      <c r="G11" s="24"/>
+      <c r="H11" s="24"/>
+      <c r="I11" s="24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="27" t="s">
+        <v>4467</v>
+      </c>
+      <c r="B12" s="24">
+        <v>193</v>
+      </c>
+      <c r="C12" t="s">
+        <v>88</v>
+      </c>
+      <c r="D12" s="24"/>
+      <c r="E12" s="24"/>
+      <c r="F12" s="24">
+        <v>1</v>
+      </c>
+      <c r="G12" s="24"/>
+      <c r="H12" s="24">
+        <v>1</v>
+      </c>
+      <c r="I12" s="24"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="27" t="s">
+        <v>4467</v>
+      </c>
+      <c r="B13" s="24">
+        <v>898</v>
+      </c>
+      <c r="C13" t="s">
+        <v>427</v>
+      </c>
+      <c r="D13" s="24">
+        <v>1</v>
+      </c>
+      <c r="E13" s="24"/>
+      <c r="F13" s="24"/>
+      <c r="G13" s="24">
+        <v>1</v>
+      </c>
+      <c r="H13" s="24"/>
+      <c r="I13" s="24"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="27" t="s">
+        <v>4467</v>
+      </c>
+      <c r="B14" s="24">
+        <v>368</v>
+      </c>
+      <c r="C14" t="s">
+        <v>154</v>
+      </c>
+      <c r="D14" s="24"/>
+      <c r="E14" s="24">
+        <v>1</v>
+      </c>
+      <c r="F14" s="24"/>
+      <c r="G14" s="24"/>
+      <c r="H14" s="24">
+        <v>1</v>
+      </c>
+      <c r="I14" s="24"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="27" t="s">
+        <v>4467</v>
+      </c>
+      <c r="B15" s="24">
+        <v>11455</v>
+      </c>
+      <c r="C15" t="s">
+        <v>2792</v>
+      </c>
+      <c r="D15" s="24"/>
+      <c r="E15" s="24">
+        <v>1</v>
+      </c>
+      <c r="F15" s="24"/>
+      <c r="G15" s="24"/>
+      <c r="H15" s="24">
+        <v>1</v>
+      </c>
+      <c r="I15" s="24"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="27" t="s">
+        <v>4467</v>
+      </c>
+      <c r="B16" s="24">
+        <v>10978</v>
+      </c>
+      <c r="C16" t="s">
+        <v>2546</v>
+      </c>
+      <c r="D16" s="24"/>
+      <c r="E16" s="24">
+        <v>1</v>
+      </c>
+      <c r="F16" s="24"/>
+      <c r="G16" s="24">
+        <v>1</v>
+      </c>
+      <c r="H16" s="24"/>
+      <c r="I16" s="24"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="27" t="s">
+        <v>4467</v>
+      </c>
+      <c r="B17" s="24">
+        <v>11912</v>
+      </c>
+      <c r="C17" t="s">
+        <v>3059</v>
+      </c>
+      <c r="D17" s="24"/>
+      <c r="E17" s="24">
+        <v>1</v>
+      </c>
+      <c r="F17" s="24"/>
+      <c r="G17" s="24"/>
+      <c r="H17" s="24">
+        <v>1</v>
+      </c>
+      <c r="I17" s="24"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="27" t="s">
+        <v>4467</v>
+      </c>
+      <c r="B18" s="24">
+        <v>10749</v>
+      </c>
+      <c r="C18" t="s">
+        <v>2440</v>
+      </c>
+      <c r="D18" s="24"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="24">
+        <v>1</v>
+      </c>
+      <c r="G18" s="24"/>
+      <c r="H18" s="24"/>
+      <c r="I18" s="24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="27" t="s">
+        <v>4468</v>
+      </c>
+      <c r="B20">
+        <v>2368</v>
+      </c>
+      <c r="C20" t="s">
+        <v>995</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="F20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" s="27" t="s">
+        <v>4468</v>
+      </c>
+      <c r="B21">
+        <v>4089</v>
+      </c>
+      <c r="C21" t="s">
+        <v>1627</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
+      <c r="I21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" s="27" t="s">
+        <v>4468</v>
+      </c>
+      <c r="B22">
+        <v>4381</v>
+      </c>
+      <c r="C22" t="s">
+        <v>1777</v>
+      </c>
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" s="27" t="s">
+        <v>4468</v>
+      </c>
+      <c r="B23">
+        <v>239</v>
+      </c>
+      <c r="C23" t="s">
+        <v>103</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" s="27" t="s">
+        <v>4468</v>
+      </c>
+      <c r="B24">
+        <v>181</v>
+      </c>
+      <c r="C24" t="s">
+        <v>82</v>
+      </c>
+      <c r="D24">
+        <v>1</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" s="27" t="s">
+        <v>4468</v>
+      </c>
+      <c r="B25">
+        <v>2365</v>
+      </c>
+      <c r="C25" t="s">
+        <v>992</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" s="27" t="s">
+        <v>4468</v>
+      </c>
+      <c r="B26">
+        <v>2240</v>
+      </c>
+      <c r="C26" t="s">
+        <v>946</v>
+      </c>
+      <c r="E26">
+        <v>1</v>
+      </c>
+      <c r="H26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" s="27" t="s">
+        <v>4468</v>
+      </c>
+      <c r="B27">
+        <v>9295</v>
+      </c>
+      <c r="C27" t="s">
+        <v>2072</v>
+      </c>
+      <c r="E27">
+        <v>1</v>
+      </c>
+      <c r="H27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" s="27" t="s">
+        <v>4468</v>
+      </c>
+      <c r="B28">
+        <v>3771</v>
+      </c>
+      <c r="C28" t="s">
+        <v>1478</v>
+      </c>
+      <c r="E28">
+        <v>1</v>
+      </c>
+      <c r="H28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" s="27" t="s">
+        <v>4468</v>
+      </c>
+      <c r="B29">
+        <v>1450</v>
+      </c>
+      <c r="C29" t="s">
+        <v>679</v>
+      </c>
+      <c r="E29">
+        <v>1</v>
+      </c>
+      <c r="H29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" s="27" t="s">
+        <v>4468</v>
+      </c>
+      <c r="B30">
+        <v>1230</v>
+      </c>
+      <c r="C30" t="s">
+        <v>605</v>
+      </c>
+      <c r="F30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" s="27" t="s">
+        <v>4468</v>
+      </c>
+      <c r="B31">
+        <v>595</v>
+      </c>
+      <c r="C31" t="s">
+        <v>234</v>
+      </c>
+      <c r="F31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32" s="27" t="s">
+        <v>4468</v>
+      </c>
+      <c r="B32">
+        <v>317</v>
+      </c>
+      <c r="C32" t="s">
+        <v>124</v>
+      </c>
+      <c r="F32">
+        <v>1</v>
+      </c>
+      <c r="I32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33" s="27" t="s">
+        <v>4468</v>
+      </c>
+      <c r="B33">
+        <v>9296</v>
+      </c>
+      <c r="C33" t="s">
+        <v>2075</v>
+      </c>
+      <c r="E33">
+        <v>1</v>
+      </c>
+      <c r="H33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34" s="27" t="s">
+        <v>4468</v>
+      </c>
+      <c r="B34">
+        <v>11268</v>
+      </c>
+      <c r="C34" t="s">
+        <v>2705</v>
+      </c>
+      <c r="D34">
+        <v>1</v>
+      </c>
+      <c r="G34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35" s="27" t="s">
+        <v>4468</v>
+      </c>
+      <c r="B35">
+        <v>11163</v>
+      </c>
+      <c r="C35" t="s">
+        <v>2636</v>
+      </c>
+      <c r="E35">
+        <v>1</v>
+      </c>
+      <c r="H35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36" s="27" t="s">
+        <v>4468</v>
+      </c>
+      <c r="B36">
+        <v>11844</v>
+      </c>
+      <c r="C36" t="s">
+        <v>3014</v>
+      </c>
+      <c r="F36">
+        <v>1</v>
+      </c>
+      <c r="I36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A37" s="27" t="s">
+        <v>4468</v>
+      </c>
+      <c r="B37">
+        <v>9595</v>
+      </c>
+      <c r="C37" t="s">
+        <v>2357</v>
+      </c>
+      <c r="D37">
+        <v>1</v>
+      </c>
+      <c r="G37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A39" s="27" t="s">
+        <v>4469</v>
+      </c>
+      <c r="B39">
+        <v>4057</v>
+      </c>
+      <c r="C39" t="s">
+        <v>1617</v>
+      </c>
+      <c r="E39">
+        <v>1</v>
+      </c>
+      <c r="H39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A40" s="27" t="s">
+        <v>4469</v>
+      </c>
+      <c r="B40">
+        <v>3249</v>
+      </c>
+      <c r="C40" t="s">
+        <v>1255</v>
+      </c>
+      <c r="F40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A41" s="27" t="s">
+        <v>4469</v>
+      </c>
+      <c r="B41">
+        <v>1708</v>
+      </c>
+      <c r="C41" t="s">
+        <v>783</v>
+      </c>
+      <c r="I41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A42" s="27" t="s">
+        <v>4469</v>
+      </c>
+      <c r="B42">
+        <v>9326</v>
+      </c>
+      <c r="C42" t="s">
+        <v>2114</v>
+      </c>
+      <c r="F42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A43" s="27" t="s">
+        <v>4469</v>
+      </c>
+      <c r="B43">
+        <v>1875</v>
+      </c>
+      <c r="C43" t="s">
+        <v>843</v>
+      </c>
+      <c r="D43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A44" s="27" t="s">
+        <v>4469</v>
+      </c>
+      <c r="B44">
+        <v>1142</v>
+      </c>
+      <c r="C44" t="s">
+        <v>567</v>
+      </c>
+      <c r="E44">
+        <v>1</v>
+      </c>
+      <c r="G44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A45" s="27" t="s">
+        <v>4469</v>
+      </c>
+      <c r="B45">
+        <v>3765</v>
+      </c>
+      <c r="C45" t="s">
+        <v>3886</v>
+      </c>
+      <c r="G45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A46" s="27" t="s">
+        <v>4469</v>
+      </c>
+      <c r="B46">
+        <v>1998</v>
+      </c>
+      <c r="C46" t="s">
+        <v>873</v>
+      </c>
+      <c r="F46">
+        <v>1</v>
+      </c>
+      <c r="H46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A47" s="27" t="s">
+        <v>4469</v>
+      </c>
+      <c r="B47">
+        <v>1963</v>
+      </c>
+      <c r="C47" t="s">
+        <v>858</v>
+      </c>
+      <c r="E47">
+        <v>1</v>
+      </c>
+      <c r="G47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A48" s="27" t="s">
+        <v>4469</v>
+      </c>
+      <c r="B48">
+        <v>11220</v>
+      </c>
+      <c r="C48" t="s">
+        <v>2672</v>
+      </c>
+      <c r="D48">
+        <v>1</v>
+      </c>
+      <c r="H48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A49" s="27" t="s">
+        <v>4469</v>
+      </c>
+      <c r="B49">
+        <v>10752</v>
+      </c>
+      <c r="C49" t="s">
+        <v>2446</v>
+      </c>
+      <c r="D49">
+        <v>1</v>
+      </c>
+      <c r="E49">
+        <v>1</v>
+      </c>
+      <c r="G49">
+        <v>1</v>
+      </c>
+      <c r="H49">
+        <v>1</v>
+      </c>
+      <c r="I49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A50" s="27" t="s">
+        <v>4469</v>
+      </c>
+      <c r="B50">
+        <v>2385</v>
+      </c>
+      <c r="C50" t="s">
+        <v>1001</v>
+      </c>
+      <c r="F50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A51" s="27" t="s">
+        <v>4469</v>
+      </c>
+      <c r="B51">
+        <v>4002</v>
+      </c>
+      <c r="C51" t="s">
+        <v>1587</v>
+      </c>
+      <c r="D51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A52" s="27" t="s">
+        <v>4470</v>
+      </c>
+      <c r="B52">
+        <v>884</v>
+      </c>
+      <c r="C52" t="s">
+        <v>412</v>
+      </c>
+      <c r="D52">
+        <v>6</v>
+      </c>
+      <c r="F52">
+        <v>1</v>
+      </c>
+      <c r="H52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A53" s="27" t="s">
+        <v>4470</v>
+      </c>
+      <c r="B53">
+        <v>3776</v>
+      </c>
+      <c r="C53" t="s">
+        <v>1484</v>
+      </c>
+      <c r="E53">
+        <v>1</v>
+      </c>
+      <c r="G53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A54" s="27" t="s">
+        <v>4470</v>
+      </c>
+      <c r="B54">
+        <v>4028</v>
+      </c>
+      <c r="C54" t="s">
+        <v>1605</v>
+      </c>
+      <c r="D54">
+        <v>3</v>
+      </c>
+      <c r="F54">
+        <v>1</v>
+      </c>
+      <c r="H54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A55" s="27" t="s">
+        <v>4470</v>
+      </c>
+      <c r="B55">
+        <v>3078</v>
+      </c>
+      <c r="C55" t="s">
+        <v>1196</v>
+      </c>
+      <c r="E55">
+        <v>1</v>
+      </c>
+      <c r="G55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A56" s="27" t="s">
+        <v>4470</v>
+      </c>
+      <c r="B56">
+        <v>5158</v>
+      </c>
+      <c r="C56" t="s">
+        <v>2045</v>
+      </c>
+      <c r="G56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A57" s="27" t="s">
+        <v>4470</v>
+      </c>
+      <c r="B57">
+        <v>5192</v>
+      </c>
+      <c r="C57" t="s">
+        <v>2060</v>
+      </c>
+      <c r="D57">
+        <v>2</v>
+      </c>
+      <c r="F57">
+        <v>1</v>
+      </c>
+      <c r="H57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A58" s="27" t="s">
+        <v>4470</v>
+      </c>
+      <c r="B58">
+        <v>2807</v>
+      </c>
+      <c r="C58" t="s">
+        <v>1115</v>
+      </c>
+      <c r="E58">
+        <v>1</v>
+      </c>
+      <c r="G58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A59" s="27" t="s">
+        <v>4470</v>
+      </c>
+      <c r="B59">
+        <v>11219</v>
+      </c>
+      <c r="C59" t="s">
+        <v>2669</v>
+      </c>
+      <c r="D59">
+        <v>1</v>
+      </c>
+      <c r="F59">
+        <v>1</v>
+      </c>
+      <c r="I59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A60" s="27" t="s">
+        <v>4470</v>
+      </c>
+      <c r="B60">
+        <v>11803</v>
+      </c>
+      <c r="C60" t="s">
+        <v>2993</v>
+      </c>
+      <c r="E60">
+        <v>1</v>
+      </c>
+      <c r="G60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A61" s="27" t="s">
+        <v>4470</v>
+      </c>
+      <c r="B61">
+        <v>11669</v>
+      </c>
+      <c r="C61" t="s">
+        <v>2900</v>
+      </c>
+      <c r="D61">
+        <v>4</v>
+      </c>
+      <c r="F61">
+        <v>1</v>
+      </c>
+      <c r="H61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A62" s="27" t="s">
+        <v>4470</v>
+      </c>
+      <c r="B62">
+        <v>11804</v>
+      </c>
+      <c r="C62" t="s">
+        <v>2996</v>
+      </c>
+      <c r="E62">
+        <v>1</v>
+      </c>
+      <c r="G62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A63" s="27" t="s">
+        <v>4470</v>
+      </c>
+      <c r="B63">
+        <v>11802</v>
+      </c>
+      <c r="C63" t="s">
+        <v>2990</v>
+      </c>
+      <c r="E63">
+        <v>1</v>
+      </c>
+      <c r="H63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A64" s="27" t="s">
+        <v>4470</v>
+      </c>
+      <c r="B64">
+        <v>11743</v>
+      </c>
+      <c r="C64" t="s">
+        <v>2932</v>
+      </c>
+      <c r="D64">
+        <v>5</v>
+      </c>
+      <c r="F64">
+        <v>1</v>
+      </c>
+      <c r="H64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A65" s="27" t="s">
+        <v>4471</v>
+      </c>
+      <c r="B65">
+        <v>1967</v>
+      </c>
+      <c r="C65" t="s">
+        <v>861</v>
+      </c>
+      <c r="D65">
+        <v>1</v>
+      </c>
+      <c r="G65">
+        <v>1</v>
+      </c>
+      <c r="I65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A66" s="27" t="s">
+        <v>4471</v>
+      </c>
+      <c r="B66">
+        <v>284</v>
+      </c>
+      <c r="C66" t="s">
+        <v>115</v>
+      </c>
+      <c r="D66">
+        <v>1</v>
+      </c>
+      <c r="G66">
+        <v>1</v>
+      </c>
+      <c r="I66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A67" s="27" t="s">
+        <v>4471</v>
+      </c>
+      <c r="B67">
+        <v>3643</v>
+      </c>
+      <c r="C67" t="s">
+        <v>1425</v>
+      </c>
+      <c r="D67">
+        <v>1</v>
+      </c>
+      <c r="H67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A68" s="27" t="s">
+        <v>4471</v>
+      </c>
+      <c r="B68">
+        <v>2362</v>
+      </c>
+      <c r="C68" t="s">
+        <v>989</v>
+      </c>
+      <c r="D68">
+        <v>1</v>
+      </c>
+      <c r="F68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A69" s="27" t="s">
+        <v>4471</v>
+      </c>
+      <c r="B69">
+        <v>2734</v>
+      </c>
+      <c r="C69" t="s">
+        <v>3475</v>
+      </c>
+      <c r="E69">
+        <v>1</v>
+      </c>
+      <c r="G69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A70" s="27" t="s">
+        <v>4471</v>
+      </c>
+      <c r="B70">
+        <v>9318</v>
+      </c>
+      <c r="C70" t="s">
+        <v>2099</v>
+      </c>
+      <c r="D70">
+        <v>1</v>
+      </c>
+      <c r="G70">
+        <v>1</v>
+      </c>
+      <c r="I70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A71" s="27" t="s">
+        <v>4471</v>
+      </c>
+      <c r="B71">
+        <v>153</v>
+      </c>
+      <c r="C71" t="s">
+        <v>74</v>
+      </c>
+      <c r="D71">
+        <v>1</v>
+      </c>
+      <c r="F71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A72" s="27" t="s">
+        <v>4471</v>
+      </c>
+      <c r="B72">
+        <v>2292</v>
+      </c>
+      <c r="C72" t="s">
+        <v>958</v>
+      </c>
+      <c r="H72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A73" s="27" t="s">
+        <v>4471</v>
+      </c>
+      <c r="B73">
+        <v>631</v>
+      </c>
+      <c r="C73" t="s">
+        <v>252</v>
+      </c>
+      <c r="F73">
+        <v>1</v>
+      </c>
+      <c r="H73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A74" s="27" t="s">
+        <v>4471</v>
+      </c>
+      <c r="B74">
+        <v>762</v>
+      </c>
+      <c r="C74" t="s">
+        <v>327</v>
+      </c>
+      <c r="F74">
+        <v>1</v>
+      </c>
+      <c r="H74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A75" s="27" t="s">
+        <v>4471</v>
+      </c>
+      <c r="B75">
+        <v>709</v>
+      </c>
+      <c r="C75" t="s">
+        <v>282</v>
+      </c>
+      <c r="E75">
+        <v>1</v>
+      </c>
+      <c r="G75">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A76" s="27" t="s">
+        <v>4471</v>
+      </c>
+      <c r="B76">
+        <v>2726</v>
+      </c>
+      <c r="C76" t="s">
+        <v>1082</v>
+      </c>
+      <c r="F76">
+        <v>1</v>
+      </c>
+      <c r="H76">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A77" s="27" t="s">
+        <v>4471</v>
+      </c>
+      <c r="B77">
+        <v>2355</v>
+      </c>
+      <c r="C77" t="s">
+        <v>983</v>
+      </c>
+      <c r="E77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A78" s="27" t="s">
+        <v>4471</v>
+      </c>
+      <c r="B78">
+        <v>2126</v>
+      </c>
+      <c r="C78" t="s">
+        <v>920</v>
+      </c>
+      <c r="F78">
+        <v>1</v>
+      </c>
+      <c r="I78">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A79" s="27" t="s">
+        <v>4471</v>
+      </c>
+      <c r="B79">
+        <v>11037</v>
+      </c>
+      <c r="C79" t="s">
+        <v>2555</v>
+      </c>
+      <c r="E79">
+        <v>1</v>
+      </c>
+      <c r="G79">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A80" s="27" t="s">
+        <v>4471</v>
+      </c>
+      <c r="B80">
+        <v>9630</v>
+      </c>
+      <c r="C80" t="s">
+        <v>2409</v>
+      </c>
+      <c r="E80">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A81" s="27" t="s">
+        <v>4471</v>
+      </c>
+      <c r="B81">
+        <v>11703</v>
+      </c>
+      <c r="C81" t="s">
+        <v>2912</v>
+      </c>
+      <c r="E81">
+        <v>1</v>
+      </c>
+      <c r="H81">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A82" s="27" t="s">
+        <v>4472</v>
+      </c>
+      <c r="B82">
+        <v>931</v>
+      </c>
+      <c r="C82" t="s">
+        <v>439</v>
+      </c>
+      <c r="E82">
+        <v>1</v>
+      </c>
+      <c r="H82">
+        <v>1</v>
+      </c>
+      <c r="I82">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A83" s="27" t="s">
+        <v>4472</v>
+      </c>
+      <c r="B83">
+        <v>719</v>
+      </c>
+      <c r="C83" t="s">
+        <v>294</v>
+      </c>
+      <c r="E83">
+        <v>1</v>
+      </c>
+      <c r="G83">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A84" s="27" t="s">
+        <v>4472</v>
+      </c>
+      <c r="B84">
+        <v>718</v>
+      </c>
+      <c r="C84" t="s">
+        <v>291</v>
+      </c>
+      <c r="D84">
+        <v>1</v>
+      </c>
+      <c r="F84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A85" s="27" t="s">
+        <v>4472</v>
+      </c>
+      <c r="B85">
+        <v>2279</v>
+      </c>
+      <c r="C85" t="s">
+        <v>955</v>
+      </c>
+      <c r="D85">
+        <v>1</v>
+      </c>
+      <c r="G85">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A86" s="27" t="s">
+        <v>4472</v>
+      </c>
+      <c r="B86">
+        <v>715</v>
+      </c>
+      <c r="C86" t="s">
+        <v>288</v>
+      </c>
+      <c r="D86">
+        <v>1</v>
+      </c>
+      <c r="G86">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A87" s="27" t="s">
+        <v>4472</v>
+      </c>
+      <c r="B87">
+        <v>803</v>
+      </c>
+      <c r="C87" t="s">
+        <v>354</v>
+      </c>
+      <c r="E87">
+        <v>1</v>
+      </c>
+      <c r="G87">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A88" s="27" t="s">
+        <v>4472</v>
+      </c>
+      <c r="B88">
+        <v>9319</v>
+      </c>
+      <c r="C88" t="s">
+        <v>2102</v>
+      </c>
+      <c r="D88">
+        <v>1</v>
+      </c>
+      <c r="F88">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A89" s="27" t="s">
+        <v>4472</v>
+      </c>
+      <c r="B89">
+        <v>677</v>
+      </c>
+      <c r="C89" t="s">
+        <v>267</v>
+      </c>
+      <c r="F89">
+        <v>1</v>
+      </c>
+      <c r="H89">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A90" s="27" t="s">
+        <v>4472</v>
+      </c>
+      <c r="B90">
+        <v>251</v>
+      </c>
+      <c r="C90" t="s">
+        <v>109</v>
+      </c>
+      <c r="D90">
+        <v>1</v>
+      </c>
+      <c r="F90">
+        <v>1</v>
+      </c>
+      <c r="H90">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A91" s="27" t="s">
+        <v>4472</v>
+      </c>
+      <c r="B91">
+        <v>611</v>
+      </c>
+      <c r="C91" t="s">
+        <v>243</v>
+      </c>
+      <c r="E91">
+        <v>1</v>
+      </c>
+      <c r="H91">
+        <v>1</v>
+      </c>
+      <c r="I91">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A92" s="27" t="s">
+        <v>4472</v>
+      </c>
+      <c r="B92">
+        <v>658</v>
+      </c>
+      <c r="C92" t="s">
+        <v>258</v>
+      </c>
+      <c r="E92">
+        <v>1</v>
+      </c>
+      <c r="G92">
+        <v>1</v>
+      </c>
+      <c r="I92">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A93" s="27" t="s">
+        <v>4472</v>
+      </c>
+      <c r="B93">
+        <v>620</v>
+      </c>
+      <c r="C93" t="s">
+        <v>246</v>
+      </c>
+      <c r="E93">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A94" s="27" t="s">
+        <v>4472</v>
+      </c>
+      <c r="B94">
+        <v>11412</v>
+      </c>
+      <c r="C94" t="s">
+        <v>2777</v>
+      </c>
+      <c r="D94">
+        <v>1</v>
+      </c>
+      <c r="G94">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A95" s="27" t="s">
+        <v>4472</v>
+      </c>
+      <c r="B95">
+        <v>11354</v>
+      </c>
+      <c r="C95" t="s">
+        <v>3486</v>
+      </c>
+      <c r="F95">
+        <v>1</v>
+      </c>
+      <c r="H95">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A96" s="27" t="s">
+        <v>4472</v>
+      </c>
+      <c r="B96">
+        <v>9597</v>
+      </c>
+      <c r="C96" t="s">
+        <v>2363</v>
+      </c>
+      <c r="F96">
+        <v>1</v>
+      </c>
+      <c r="H96">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
